--- a/output/pdf_financials_xlsx/HHE.xlsx
+++ b/output/pdf_financials_xlsx/HHE.xlsx
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.896574</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.712932</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.808217</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.281684</v>
       </c>
     </row>
     <row r="93">
@@ -3458,7 +3458,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3740,7 +3744,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.896574</v>
       </c>

--- a/output/pdf_financials_xlsx/HHE.xlsx
+++ b/output/pdf_financials_xlsx/HHE.xlsx
@@ -4600,7 +4600,11 @@
           <t>– Shares issued for cash 3,367,500 843,000</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5864,7 +5868,11 @@
           <t>– Shares issued for cash 33,675,000 843,000</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
